--- a/115年3月誠品及博客來的月排行榜書籍清單-1.xlsx
+++ b/115年3月誠品及博客來的月排行榜書籍清單-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\我的雲端硬碟\lbk\工作\1. 每日工作内容整理\1150304_開發撈每月誠品與博客來中文紙本圖書排行榜，並比對是否有館藏後提供採編組採購\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66BD931-A148-4EED-B8FB-9BED8BE559B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091D1B0D-1E34-4064-A462-01269861921D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3680" yWindow="3680" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="115年3月" sheetId="1" r:id="rId1"/>
